--- a/Images/2/Analytics.xlsx
+++ b/Images/2/Analytics.xlsx
@@ -448,19 +448,19 @@
         <v>6</v>
       </c>
       <c r="C4" s="2">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="D4" s="2">
-        <v>0.1000000000000001</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>1.99</v>
+        <v>2.52</v>
       </c>
       <c r="G4" s="2">
-        <v>0.1845238095238093</v>
+        <v>0.2460317460317463</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -469,17 +469,17 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="2">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="D5" s="2">
-        <v>0.004166666666666763</v>
+        <v>0.03333333333333337</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="2">
-        <v>1.294848484848485</v>
+        <v>2.48</v>
       </c>
       <c r="G5" s="2">
-        <v>0.2292568542568542</v>
+        <v>0.02789802789802742</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -488,17 +488,17 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="2">
-        <v>2.406</v>
+        <v>2.412</v>
       </c>
       <c r="D6" s="2">
-        <v>0.002500000000000095</v>
+        <v>0.005000000000000004</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="2">
-        <v>1.704573146292597</v>
+        <v>2.412</v>
       </c>
       <c r="G6" s="2">
-        <v>0.01462687279321283</v>
+        <v>0.115936635175111</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -507,17 +507,17 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="2">
-        <v>2.347</v>
+        <v>2.385</v>
       </c>
       <c r="D7" s="2">
-        <v>0.02208333333333331</v>
+        <v>0.006250000000000052</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="2">
-        <v>1.666257257257262</v>
+        <v>2.385</v>
       </c>
       <c r="G7" s="2">
-        <v>0.008180204013534333</v>
+        <v>0.0348294723294582</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -526,17 +526,17 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="2">
-        <v>2.4003079</v>
+        <v>2.3998611</v>
       </c>
       <c r="D8" s="2">
-        <v>0.0001282916666667244</v>
+        <v>5.787500000002203E-05</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="2">
-        <v>1.679287053145754</v>
+        <v>2.3998611</v>
       </c>
       <c r="G8" s="2">
-        <v>0.0004243731275272154</v>
+        <v>0.000190933669649179</v>
       </c>
     </row>
   </sheetData>

--- a/Images/2/Analytics.xlsx
+++ b/Images/2/Analytics.xlsx
@@ -448,19 +448,19 @@
         <v>6</v>
       </c>
       <c r="C4" s="2">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="D4" s="2">
-        <v>0.05000000000000004</v>
+        <v>0.03333333333333337</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="F4" s="2">
-        <v>2.52</v>
+        <v>1.843333333333334</v>
       </c>
       <c r="G4" s="2">
-        <v>0.2460317460317463</v>
+        <v>0.09722222222222249</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -469,17 +469,17 @@
       </c>
       <c r="B5" s="1"/>
       <c r="C5" s="2">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="D5" s="2">
-        <v>0.03333333333333337</v>
+        <v>0.01666666666666668</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="2">
-        <v>2.48</v>
+        <v>1.4610101010101</v>
       </c>
       <c r="G5" s="2">
-        <v>0.02789802789802742</v>
+        <v>0.1303511303511308</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -488,17 +488,17 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="2">
-        <v>2.412</v>
+        <v>2.386</v>
       </c>
       <c r="D6" s="2">
-        <v>0.005000000000000004</v>
+        <v>0.005833333333333246</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" s="2">
-        <v>2.412</v>
+        <v>1.644292585170335</v>
       </c>
       <c r="G6" s="2">
-        <v>0.115936635175111</v>
+        <v>0.02125441358908604</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -507,17 +507,17 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="2">
-        <v>2.385</v>
+        <v>2.272</v>
       </c>
       <c r="D7" s="2">
-        <v>0.006250000000000052</v>
+        <v>0.05333333333333339</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" s="2">
-        <v>2.385</v>
+        <v>1.645661661661669</v>
       </c>
       <c r="G7" s="2">
-        <v>0.0348294723294582</v>
+        <v>0.02043948710614947</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -526,17 +526,17 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="2">
-        <v>2.3998611</v>
+        <v>2.4004547</v>
       </c>
       <c r="D8" s="2">
-        <v>5.787500000002203E-05</v>
+        <v>0.0001894583333333921</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="2">
-        <v>2.3998611</v>
+        <v>1.68005210113037</v>
       </c>
       <c r="G8" s="2">
-        <v>0.000190933669649179</v>
+        <v>3.101257760106972E-05</v>
       </c>
     </row>
   </sheetData>

--- a/Images/2/Analytics.xlsx
+++ b/Images/2/Analytics.xlsx
@@ -34,16 +34,19 @@
     <t>Оценка дисперсии Dx</t>
   </si>
   <si>
-    <t>2.400000</t>
-  </si>
-  <si>
-    <t>1.680000</t>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>1.68</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <sz val="11"/>
@@ -96,12 +99,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -396,7 +400,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -447,20 +451,20 @@
       <c r="B4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="2">
-        <v>2.48</v>
-      </c>
-      <c r="D4" s="2">
-        <v>0.03333333333333337</v>
+      <c r="C4" s="3">
+        <v>2.24</v>
+      </c>
+      <c r="D4" s="3">
+        <v>6.666666666666654</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="2">
-        <v>1.843333333333334</v>
-      </c>
-      <c r="G4" s="2">
-        <v>0.09722222222222249</v>
+      <c r="F4" s="3">
+        <v>1.69</v>
+      </c>
+      <c r="G4" s="3">
+        <v>0.595238095238109</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -468,18 +472,18 @@
         <v>100</v>
       </c>
       <c r="B5" s="1"/>
-      <c r="C5" s="2">
-        <v>2.44</v>
-      </c>
-      <c r="D5" s="2">
-        <v>0.01666666666666668</v>
+      <c r="C5" s="3">
+        <v>2.58</v>
+      </c>
+      <c r="D5" s="3">
+        <v>7.500000000000007</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="2">
-        <v>1.4610101010101</v>
-      </c>
-      <c r="G5" s="2">
-        <v>0.1303511303511308</v>
+      <c r="F5" s="3">
+        <v>1.478383838383838</v>
+      </c>
+      <c r="G5" s="3">
+        <v>12.00096200096201</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -487,18 +491,18 @@
         <v>500</v>
       </c>
       <c r="B6" s="1"/>
-      <c r="C6" s="2">
-        <v>2.386</v>
-      </c>
-      <c r="D6" s="2">
-        <v>0.005833333333333246</v>
+      <c r="C6" s="3">
+        <v>2.388</v>
+      </c>
+      <c r="D6" s="3">
+        <v>0.5000000000000004</v>
       </c>
       <c r="E6" s="1"/>
-      <c r="F6" s="2">
-        <v>1.644292585170335</v>
-      </c>
-      <c r="G6" s="2">
-        <v>0.02125441358908604</v>
+      <c r="F6" s="3">
+        <v>1.732921843687374</v>
+      </c>
+      <c r="G6" s="3">
+        <v>3.150109743296056</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -506,37 +510,18 @@
         <v>1000</v>
       </c>
       <c r="B7" s="1"/>
-      <c r="C7" s="2">
-        <v>2.272</v>
-      </c>
-      <c r="D7" s="2">
-        <v>0.05333333333333339</v>
+      <c r="C7" s="3">
+        <v>2.453</v>
+      </c>
+      <c r="D7" s="3">
+        <v>2.208333333333331</v>
       </c>
       <c r="E7" s="1"/>
-      <c r="F7" s="2">
-        <v>1.645661661661669</v>
-      </c>
-      <c r="G7" s="2">
-        <v>0.02043948710614947</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="2">
-        <v>10000000</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="2">
-        <v>2.4004547</v>
-      </c>
-      <c r="D8" s="2">
-        <v>0.0001894583333333921</v>
-      </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="2">
-        <v>1.68005210113037</v>
-      </c>
-      <c r="G8" s="2">
-        <v>3.101257760106972E-05</v>
+      <c r="F7" s="3">
+        <v>1.645436436436434</v>
+      </c>
+      <c r="G7" s="3">
+        <v>2.057354974021769</v>
       </c>
     </row>
   </sheetData>
@@ -548,8 +533,8 @@
     <mergeCell ref="E1:E3"/>
     <mergeCell ref="F1:F3"/>
     <mergeCell ref="G1:G3"/>
-    <mergeCell ref="B4:B8"/>
-    <mergeCell ref="E4:E8"/>
+    <mergeCell ref="B4:B7"/>
+    <mergeCell ref="E4:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
